--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/3.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/3.xlsx
@@ -426,13 +426,13 @@
         <v>-7.981058433746566</v>
       </c>
       <c r="E2">
-        <v>-4.413240006304772</v>
+        <v>-5.787477899516465</v>
       </c>
       <c r="F2">
-        <v>-6.675810975490217</v>
+        <v>-6.476303242546671</v>
       </c>
       <c r="G2">
-        <v>-12.13292543500056</v>
+        <v>-14.15890316248713</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-8.94810454223895</v>
       </c>
       <c r="E3">
-        <v>-4.915307391061177</v>
+        <v>-6.494236837893578</v>
       </c>
       <c r="F3">
-        <v>-6.568203978948054</v>
+        <v>-6.297336950274047</v>
       </c>
       <c r="G3">
-        <v>-11.82464081329255</v>
+        <v>-13.67938388330585</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-10.11141496072897</v>
       </c>
       <c r="E4">
-        <v>-7.14357472585343</v>
+        <v>-5.579186209059658</v>
       </c>
       <c r="F4">
-        <v>-6.844504683600725</v>
+        <v>-6.07962542947028</v>
       </c>
       <c r="G4">
-        <v>-12.07781809395386</v>
+        <v>-13.97805137022228</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-11.26558500261335</v>
       </c>
       <c r="E5">
-        <v>-6.480243853209876</v>
+        <v>-7.421754355670612</v>
       </c>
       <c r="F5">
-        <v>-6.538035252321797</v>
+        <v>-5.849022026776745</v>
       </c>
       <c r="G5">
-        <v>-11.70345829382753</v>
+        <v>-13.52349360440711</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.36900360252178</v>
       </c>
       <c r="E6">
-        <v>-7.68406168409091</v>
+        <v>-8.765633359134883</v>
       </c>
       <c r="F6">
-        <v>-6.961256442086093</v>
+        <v>-5.960405964491972</v>
       </c>
       <c r="G6">
-        <v>-11.97327106582367</v>
+        <v>-13.65058544765973</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.31984089312645</v>
       </c>
       <c r="E7">
-        <v>-7.800873671118767</v>
+        <v>-9.212747711808207</v>
       </c>
       <c r="F7">
-        <v>-6.558965197304631</v>
+        <v>-5.874199425617434</v>
       </c>
       <c r="G7">
-        <v>-10.68283696734346</v>
+        <v>-13.14580670601382</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-14.04890053934552</v>
       </c>
       <c r="E8">
-        <v>-8.849337672692661</v>
+        <v>-9.72490906512771</v>
       </c>
       <c r="F8">
-        <v>-6.422117245627347</v>
+        <v>-6.008785105917672</v>
       </c>
       <c r="G8">
-        <v>-11.73852690272503</v>
+        <v>-13.12644001460908</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-14.47074071432333</v>
       </c>
       <c r="E9">
-        <v>-8.957536502157929</v>
+        <v>-10.15787646500107</v>
       </c>
       <c r="F9">
-        <v>-5.897746597409412</v>
+        <v>-5.53221457031088</v>
       </c>
       <c r="G9">
-        <v>-11.28355200817191</v>
+        <v>-13.82306155971022</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-14.52377979537417</v>
       </c>
       <c r="E10">
-        <v>-10.49609913168596</v>
+        <v>-10.76437046037436</v>
       </c>
       <c r="F10">
-        <v>-5.82219120660007</v>
+        <v>-5.573949376798724</v>
       </c>
       <c r="G10">
-        <v>-10.8079325516359</v>
+        <v>-13.25705096776995</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-14.15449951978406</v>
       </c>
       <c r="E11">
-        <v>-12.01095972825784</v>
+        <v>-12.13581881359732</v>
       </c>
       <c r="F11">
-        <v>-5.949118630261427</v>
+        <v>-5.150502871100868</v>
       </c>
       <c r="G11">
-        <v>-10.83407592975952</v>
+        <v>-12.74974959042311</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-13.34583546493746</v>
       </c>
       <c r="E12">
-        <v>-10.79122431123984</v>
+        <v>-11.97205560805794</v>
       </c>
       <c r="F12">
-        <v>-5.86453734823118</v>
+        <v>-5.183206816163392</v>
       </c>
       <c r="G12">
-        <v>-9.923801707190441</v>
+        <v>-12.14754480410198</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.11030798627347</v>
       </c>
       <c r="E13">
-        <v>-12.57666122977002</v>
+        <v>-12.49226405968907</v>
       </c>
       <c r="F13">
-        <v>-5.883018224987637</v>
+        <v>-4.928253553664566</v>
       </c>
       <c r="G13">
-        <v>-9.61556012257444</v>
+        <v>-12.10479572955338</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.50311765486773</v>
       </c>
       <c r="E14">
-        <v>-12.70738468894945</v>
+        <v>-13.72537658892573</v>
       </c>
       <c r="F14">
-        <v>-5.621841438191578</v>
+        <v>-4.585489204631978</v>
       </c>
       <c r="G14">
-        <v>-9.565951597668461</v>
+        <v>-11.44147165148623</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-8.610267642718069</v>
       </c>
       <c r="E15">
-        <v>-12.77805605431315</v>
+        <v>-13.12117852987433</v>
       </c>
       <c r="F15">
-        <v>-5.181470558087125</v>
+        <v>-4.834203203852919</v>
       </c>
       <c r="G15">
-        <v>-9.851347107517951</v>
+        <v>-11.3691825790907</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-6.542287058453305</v>
       </c>
       <c r="E16">
-        <v>-14.15871079519371</v>
+        <v>-14.64095704921854</v>
       </c>
       <c r="F16">
-        <v>-4.950788460490323</v>
+        <v>-4.715947130164067</v>
       </c>
       <c r="G16">
-        <v>-8.812633649661763</v>
+        <v>-11.28176431358071</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-4.417872500059207</v>
       </c>
       <c r="E17">
-        <v>-13.57426593976377</v>
+        <v>-15.51964403177087</v>
       </c>
       <c r="F17">
-        <v>-5.001728085558077</v>
+        <v>-4.163521334748118</v>
       </c>
       <c r="G17">
-        <v>-8.380458482237605</v>
+        <v>-10.40588665916465</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-2.365996313179202</v>
       </c>
       <c r="E18">
-        <v>-14.76211637129376</v>
+        <v>-16.02484964901459</v>
       </c>
       <c r="F18">
-        <v>-4.543017979523045</v>
+        <v>-3.824808530682623</v>
       </c>
       <c r="G18">
-        <v>-8.148614357031366</v>
+        <v>-10.15242798213251</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.5041993716722745</v>
       </c>
       <c r="E19">
-        <v>-16.08321262202544</v>
+        <v>-16.98764397931138</v>
       </c>
       <c r="F19">
-        <v>-4.366817606008367</v>
+        <v>-3.396324722808342</v>
       </c>
       <c r="G19">
-        <v>-7.235456649297577</v>
+        <v>-10.20475777547177</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.071616735397636</v>
       </c>
       <c r="E20">
-        <v>-17.19633870395486</v>
+        <v>-17.48343489909315</v>
       </c>
       <c r="F20">
-        <v>-4.022789168319107</v>
+        <v>-3.586916323211855</v>
       </c>
       <c r="G20">
-        <v>-7.805314095154483</v>
+        <v>-10.40765117993708</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>2.295197978246536</v>
       </c>
       <c r="E21">
-        <v>-16.94121353531073</v>
+        <v>-19.40462641142528</v>
       </c>
       <c r="F21">
-        <v>-4.05825903213958</v>
+        <v>-3.108425631965374</v>
       </c>
       <c r="G21">
-        <v>-7.639866271283866</v>
+        <v>-10.21448084772061</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.123334486367827</v>
       </c>
       <c r="E22">
-        <v>-17.63437799471682</v>
+        <v>-18.81231559664402</v>
       </c>
       <c r="F22">
-        <v>-3.867018820059675</v>
+        <v>-3.025706519856621</v>
       </c>
       <c r="G22">
-        <v>-7.955119591352044</v>
+        <v>-9.766660042077854</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.546183491480992</v>
       </c>
       <c r="E23">
-        <v>-17.77596526304064</v>
+        <v>-19.70007311263371</v>
       </c>
       <c r="F23">
-        <v>-3.795999569148062</v>
+        <v>-3.014564978288968</v>
       </c>
       <c r="G23">
-        <v>-8.055177519730975</v>
+        <v>-9.102445427260641</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.583941968505902</v>
       </c>
       <c r="E24">
-        <v>-18.08108025625544</v>
+        <v>-19.58051234188319</v>
       </c>
       <c r="F24">
-        <v>-3.002702757080879</v>
+        <v>-2.615691163227755</v>
       </c>
       <c r="G24">
-        <v>-8.589357216311157</v>
+        <v>-9.530330127665902</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.276193768758707</v>
       </c>
       <c r="E25">
-        <v>-19.04089937912919</v>
+        <v>-19.80593977798502</v>
       </c>
       <c r="F25">
-        <v>-3.28415797789747</v>
+        <v>-2.996946431998825</v>
       </c>
       <c r="G25">
-        <v>-8.274329013339649</v>
+        <v>-10.42757404299241</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.674863600505034</v>
       </c>
       <c r="E26">
-        <v>-20.69753743993322</v>
+        <v>-19.76957160322942</v>
       </c>
       <c r="F26">
-        <v>-3.197480097970738</v>
+        <v>-2.593696351948623</v>
       </c>
       <c r="G26">
-        <v>-7.618423867826007</v>
+        <v>-10.07153811242596</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.84240035105685</v>
       </c>
       <c r="E27">
-        <v>-19.62295320028308</v>
+        <v>-20.08145213661169</v>
       </c>
       <c r="F27">
-        <v>-2.967270998160936</v>
+        <v>-2.488123411564034</v>
       </c>
       <c r="G27">
-        <v>-9.588013073142164</v>
+        <v>-10.00378117687369</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>0.8453629596387497</v>
       </c>
       <c r="E28">
-        <v>-19.86967352116897</v>
+        <v>-20.1315823438766</v>
       </c>
       <c r="F28">
-        <v>-2.565811848435586</v>
+        <v>-2.900956874097224</v>
       </c>
       <c r="G28">
-        <v>-9.411170351525376</v>
+        <v>-9.921219481669809</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-0.2578705583478362</v>
       </c>
       <c r="E29">
-        <v>-19.12668226225649</v>
+        <v>-19.6901512260829</v>
       </c>
       <c r="F29">
-        <v>-2.689859038637409</v>
+        <v>-2.629636728453885</v>
       </c>
       <c r="G29">
-        <v>-8.72075607931037</v>
+        <v>-9.797365351954594</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.411540595652794</v>
       </c>
       <c r="E30">
-        <v>-18.06617251982219</v>
+        <v>-20.20076836976579</v>
       </c>
       <c r="F30">
-        <v>-3.173447502880719</v>
+        <v>-2.637024108952051</v>
       </c>
       <c r="G30">
-        <v>-9.044378458501825</v>
+        <v>-10.86360599596982</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-2.563867494618944</v>
       </c>
       <c r="E31">
-        <v>-17.99722650305541</v>
+        <v>-20.50153602793323</v>
       </c>
       <c r="F31">
-        <v>-2.858045785897404</v>
+        <v>-2.797078773418763</v>
       </c>
       <c r="G31">
-        <v>-9.302147465826097</v>
+        <v>-10.20173524739441</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-3.667507692931801</v>
       </c>
       <c r="E32">
-        <v>-18.44130224966959</v>
+        <v>-19.46111006772295</v>
       </c>
       <c r="F32">
-        <v>-3.293487051587798</v>
+        <v>-2.887573770337595</v>
       </c>
       <c r="G32">
-        <v>-9.413841961775567</v>
+        <v>-10.28797495869243</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-4.679971187262935</v>
       </c>
       <c r="E33">
-        <v>-17.31462244503521</v>
+        <v>-19.52493890886106</v>
       </c>
       <c r="F33">
-        <v>-3.296019370738156</v>
+        <v>-2.499937587462761</v>
       </c>
       <c r="G33">
-        <v>-9.236664875059313</v>
+        <v>-10.41969163406341</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.558244300504865</v>
       </c>
       <c r="E34">
-        <v>-17.17887690818129</v>
+        <v>-18.79544703096544</v>
       </c>
       <c r="F34">
-        <v>-3.380631302362306</v>
+        <v>-2.379314868104111</v>
       </c>
       <c r="G34">
-        <v>-8.779150792077575</v>
+        <v>-9.491110094662156</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-6.264434424844139</v>
       </c>
       <c r="E35">
-        <v>-18.06363204590389</v>
+        <v>-18.32920440408372</v>
       </c>
       <c r="F35">
-        <v>-3.03371020570247</v>
+        <v>-2.796573469303056</v>
       </c>
       <c r="G35">
-        <v>-9.273415241090762</v>
+        <v>-10.01722199176313</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-6.769896656532493</v>
       </c>
       <c r="E36">
-        <v>-16.58549737353422</v>
+        <v>-17.52979288750967</v>
       </c>
       <c r="F36">
-        <v>-2.88517564670649</v>
+        <v>-2.847305174152706</v>
       </c>
       <c r="G36">
-        <v>-8.576412983252606</v>
+        <v>-9.767894875564004</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.056044111861054</v>
       </c>
       <c r="E37">
-        <v>-16.73456568091871</v>
+        <v>-17.99653364653224</v>
       </c>
       <c r="F37">
-        <v>-3.676743656004031</v>
+        <v>-2.731142384890728</v>
       </c>
       <c r="G37">
-        <v>-8.728380265687312</v>
+        <v>-9.229782250883169</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.116340349661536</v>
       </c>
       <c r="E38">
-        <v>-15.74698248390393</v>
+        <v>-17.47624821084298</v>
       </c>
       <c r="F38">
-        <v>-2.884941218731498</v>
+        <v>-2.424424443390961</v>
       </c>
       <c r="G38">
-        <v>-8.477642857088451</v>
+        <v>-9.216162666534606</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-6.957823688988765</v>
       </c>
       <c r="E39">
-        <v>-15.63099467914548</v>
+        <v>-17.35552362227249</v>
       </c>
       <c r="F39">
-        <v>-2.931508720647275</v>
+        <v>-2.874021679627795</v>
       </c>
       <c r="G39">
-        <v>-8.806810400058184</v>
+        <v>-8.832592928718029</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-6.598410364291866</v>
       </c>
       <c r="E40">
-        <v>-16.28596146029686</v>
+        <v>-17.24779122563001</v>
       </c>
       <c r="F40">
-        <v>-3.281182482186614</v>
+        <v>-2.804272315944674</v>
       </c>
       <c r="G40">
-        <v>-7.994690542182952</v>
+        <v>-8.415679376229912</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-6.063857148011771</v>
       </c>
       <c r="E41">
-        <v>-14.60455264667088</v>
+        <v>-16.36375158680062</v>
       </c>
       <c r="F41">
-        <v>-2.862309392919613</v>
+        <v>-2.934461022070853</v>
       </c>
       <c r="G41">
-        <v>-7.045623346984688</v>
+        <v>-8.509189045532166</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.386705437400239</v>
       </c>
       <c r="E42">
-        <v>-14.1646657385138</v>
+        <v>-16.20500593046174</v>
       </c>
       <c r="F42">
-        <v>-3.438828254245985</v>
+        <v>-2.84849305300832</v>
       </c>
       <c r="G42">
-        <v>-7.615007384829479</v>
+        <v>-8.791058824382333</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-4.605024385029176</v>
       </c>
       <c r="E43">
-        <v>-13.66377122852538</v>
+        <v>-15.28802164322654</v>
       </c>
       <c r="F43">
-        <v>-3.218434479791954</v>
+        <v>-2.80397824551668</v>
       </c>
       <c r="G43">
-        <v>-6.844226309103125</v>
+        <v>-8.51070858593469</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.760047243607833</v>
       </c>
       <c r="E44">
-        <v>-13.61611809654266</v>
+        <v>-14.81709657422089</v>
       </c>
       <c r="F44">
-        <v>-3.48669712135156</v>
+        <v>-2.955739295546564</v>
       </c>
       <c r="G44">
-        <v>-6.616937494558923</v>
+        <v>-8.249453574157567</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.899700474403012</v>
       </c>
       <c r="E45">
-        <v>-13.12475602434039</v>
+        <v>-14.77703316467503</v>
       </c>
       <c r="F45">
-        <v>-4.098206221772183</v>
+        <v>-3.159844881759348</v>
       </c>
       <c r="G45">
-        <v>-7.517938879072508</v>
+        <v>-7.830563625982504</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.073932234130564</v>
       </c>
       <c r="E46">
-        <v>-12.44743216701314</v>
+        <v>-14.5304124702173</v>
       </c>
       <c r="F46">
-        <v>-3.675984871463067</v>
+        <v>-2.977186555972446</v>
       </c>
       <c r="G46">
-        <v>-6.357390724280061</v>
+        <v>-8.046854808245248</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.331679653786036</v>
       </c>
       <c r="E47">
-        <v>-12.38333614590857</v>
+        <v>-14.09063877391041</v>
       </c>
       <c r="F47">
-        <v>-3.883799058538184</v>
+        <v>-3.41846615511777</v>
       </c>
       <c r="G47">
-        <v>-7.447195831443822</v>
+        <v>-7.983772362994435</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-0.7154626208724534</v>
       </c>
       <c r="E48">
-        <v>-11.18006173190846</v>
+        <v>-12.68456117995079</v>
       </c>
       <c r="F48">
-        <v>-3.965766013045195</v>
+        <v>-3.551439832452161</v>
       </c>
       <c r="G48">
-        <v>-7.517872668161723</v>
+        <v>-7.957701816872675</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-0.2636969124981802</v>
       </c>
       <c r="E49">
-        <v>-10.08163054813393</v>
+        <v>-13.05340085940153</v>
       </c>
       <c r="F49">
-        <v>-4.031730566064925</v>
+        <v>-3.46106329207193</v>
       </c>
       <c r="G49">
-        <v>-6.475064065473456</v>
+        <v>-7.799821900104832</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-0.0001915580987522308</v>
       </c>
       <c r="E50">
-        <v>-11.1917180240042</v>
+        <v>-12.27220286528633</v>
       </c>
       <c r="F50">
-        <v>-4.241065635691583</v>
+        <v>-3.45323107827846</v>
       </c>
       <c r="G50">
-        <v>-7.198981058545886</v>
+        <v>-7.188933552834198</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>0.06773136343224916</v>
       </c>
       <c r="E51">
-        <v>-11.3193621208584</v>
+        <v>-12.22538750099504</v>
       </c>
       <c r="F51">
-        <v>-4.405767441288</v>
+        <v>-3.807818715251205</v>
       </c>
       <c r="G51">
-        <v>-6.786530121444707</v>
+        <v>-7.875140121668791</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-0.05319974336781515</v>
       </c>
       <c r="E52">
-        <v>-10.96116888379969</v>
+        <v>-11.33841341100867</v>
       </c>
       <c r="F52">
-        <v>-4.57376614914756</v>
+        <v>-3.634469582336964</v>
       </c>
       <c r="G52">
-        <v>-6.294348005575721</v>
+        <v>-7.795455290538533</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-0.3464082780118066</v>
       </c>
       <c r="E53">
-        <v>-10.36372730796774</v>
+        <v>-10.81176094086463</v>
       </c>
       <c r="F53">
-        <v>-4.298237068730597</v>
+        <v>-3.539718433702548</v>
       </c>
       <c r="G53">
-        <v>-6.537832008898038</v>
+        <v>-7.726125845855116</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-0.7831402924444693</v>
       </c>
       <c r="E54">
-        <v>-10.22670474144365</v>
+        <v>-11.47027351716402</v>
       </c>
       <c r="F54">
-        <v>-4.456285427347728</v>
+        <v>-3.642576814108163</v>
       </c>
       <c r="G54">
-        <v>-6.643733050153783</v>
+        <v>-8.16263120684464</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.325836961961087</v>
       </c>
       <c r="E55">
-        <v>-8.684012143620633</v>
+        <v>-10.74139298325944</v>
       </c>
       <c r="F55">
-        <v>-4.629288302687599</v>
+        <v>-3.799511018568529</v>
       </c>
       <c r="G55">
-        <v>-6.787364378920604</v>
+        <v>-7.88558820339073</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.935653231810221</v>
       </c>
       <c r="E56">
-        <v>-9.566190579632872</v>
+        <v>-10.80472369225671</v>
       </c>
       <c r="F56">
-        <v>-4.567998226921866</v>
+        <v>-4.133191490662018</v>
       </c>
       <c r="G56">
-        <v>-6.807356763432262</v>
+        <v>-8.008392890169995</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.57255634287885</v>
       </c>
       <c r="E57">
-        <v>-8.114615407318185</v>
+        <v>-9.623765598166392</v>
       </c>
       <c r="F57">
-        <v>-4.626187723498921</v>
+        <v>-4.028715308718735</v>
       </c>
       <c r="G57">
-        <v>-7.423942559575981</v>
+        <v>-7.591088693308245</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.197336064849188</v>
       </c>
       <c r="E58">
-        <v>-8.771710571253177</v>
+        <v>-10.38509264833593</v>
       </c>
       <c r="F58">
-        <v>-4.427159201097894</v>
+        <v>-4.207390015665575</v>
       </c>
       <c r="G58">
-        <v>-7.414106928778807</v>
+        <v>-7.760353576185641</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.775092338457607</v>
       </c>
       <c r="E59">
-        <v>-6.880950404252595</v>
+        <v>-8.627111867714254</v>
       </c>
       <c r="F59">
-        <v>-4.302430264523568</v>
+        <v>-3.958914586256641</v>
       </c>
       <c r="G59">
-        <v>-6.878871168171599</v>
+        <v>-7.25901449135503</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.281523536423162</v>
       </c>
       <c r="E60">
-        <v>-7.175921615690219</v>
+        <v>-9.192912995654611</v>
       </c>
       <c r="F60">
-        <v>-5.133660505067148</v>
+        <v>-4.096533747985931</v>
       </c>
       <c r="G60">
-        <v>-7.408336647903857</v>
+        <v>-7.879592805419111</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.698854802989239</v>
       </c>
       <c r="E61">
-        <v>-6.593917607750417</v>
+        <v>-9.091538576518904</v>
       </c>
       <c r="F61">
-        <v>-4.776218314024356</v>
+        <v>-4.318828625629386</v>
       </c>
       <c r="G61">
-        <v>-7.519604083478762</v>
+        <v>-8.372920370044685</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.016773115811819</v>
       </c>
       <c r="E62">
-        <v>-6.18543113836252</v>
+        <v>-8.340559089456889</v>
       </c>
       <c r="F62">
-        <v>-4.86805443776832</v>
+        <v>-4.411480691265108</v>
       </c>
       <c r="G62">
-        <v>-6.943380458549837</v>
+        <v>-8.123712433484968</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.230744784739972</v>
       </c>
       <c r="E63">
-        <v>-7.584860932478883</v>
+        <v>-8.69608958379909</v>
       </c>
       <c r="F63">
-        <v>-4.896296795999366</v>
+        <v>-4.24771659756866</v>
       </c>
       <c r="G63">
-        <v>-8.160641568975539</v>
+        <v>-8.370917489993426</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.343176085837098</v>
       </c>
       <c r="E64">
-        <v>-6.810265453466869</v>
+        <v>-7.454214457357593</v>
       </c>
       <c r="F64">
-        <v>-5.012971516316274</v>
+        <v>-4.486524979386924</v>
       </c>
       <c r="G64">
-        <v>-7.938047108006022</v>
+        <v>-7.742152196810728</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.35921167629032</v>
       </c>
       <c r="E65">
-        <v>-6.625444843791819</v>
+        <v>-8.03414895267589</v>
       </c>
       <c r="F65">
-        <v>-4.877436526972428</v>
+        <v>-4.389171100372912</v>
       </c>
       <c r="G65">
-        <v>-7.645265771058417</v>
+        <v>-8.534117453442878</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.287166606162855</v>
       </c>
       <c r="E66">
-        <v>-6.561439392167405</v>
+        <v>-8.306341939854931</v>
       </c>
       <c r="F66">
-        <v>-5.013375759608841</v>
+        <v>-4.310899492849789</v>
       </c>
       <c r="G66">
-        <v>-7.855713840444348</v>
+        <v>-8.390846974139839</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-5.13839062356281</v>
       </c>
       <c r="E67">
-        <v>-4.627785519366171</v>
+        <v>-8.161073022162874</v>
       </c>
       <c r="F67">
-        <v>-5.011892153590426</v>
+        <v>-4.423830820873446</v>
       </c>
       <c r="G67">
-        <v>-8.210577837889904</v>
+        <v>-8.574790815938364</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.928555709884749</v>
       </c>
       <c r="E68">
-        <v>-6.292230669359418</v>
+        <v>-8.051320926112975</v>
       </c>
       <c r="F68">
-        <v>-5.072454922776501</v>
+        <v>-4.251838553764991</v>
       </c>
       <c r="G68">
-        <v>-7.075560610296317</v>
+        <v>-8.181051082225144</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.674684047847298</v>
       </c>
       <c r="E69">
-        <v>-5.376758892442786</v>
+        <v>-6.730989987488591</v>
       </c>
       <c r="F69">
-        <v>-5.334913193944691</v>
+        <v>-4.546338076073465</v>
       </c>
       <c r="G69">
-        <v>-7.117435700822559</v>
+        <v>-8.045335267842722</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.393513465945515</v>
       </c>
       <c r="E70">
-        <v>-6.621957918805912</v>
+        <v>-7.509919216125946</v>
       </c>
       <c r="F70">
-        <v>-5.204298706973473</v>
+        <v>-4.509459159300831</v>
       </c>
       <c r="G70">
-        <v>-7.021227936905799</v>
+        <v>-8.518081170850648</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.100054771448458</v>
       </c>
       <c r="E71">
-        <v>-6.525247827898104</v>
+        <v>-7.81663276066546</v>
       </c>
       <c r="F71">
-        <v>-5.539061855262421</v>
+        <v>-4.95296209655527</v>
       </c>
       <c r="G71">
-        <v>-7.439048578871676</v>
+        <v>-7.724338151263909</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.809302488585816</v>
       </c>
       <c r="E72">
-        <v>-5.887086213789182</v>
+        <v>-7.419811640321321</v>
       </c>
       <c r="F72">
-        <v>-5.48820258183274</v>
+        <v>-4.73400968138211</v>
       </c>
       <c r="G72">
-        <v>-7.146356626653632</v>
+        <v>-7.800288687025869</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.532995379921697</v>
       </c>
       <c r="E73">
-        <v>-6.410867631412366</v>
+        <v>-8.201159074078772</v>
       </c>
       <c r="F73">
-        <v>-5.565537305823296</v>
+        <v>-4.616212523234409</v>
       </c>
       <c r="G73">
-        <v>-6.732429186241937</v>
+        <v>-7.995726742936744</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.278281587201691</v>
       </c>
       <c r="E74">
-        <v>-6.867808772682336</v>
+        <v>-8.102891188112325</v>
       </c>
       <c r="F74">
-        <v>-5.461736243313295</v>
+        <v>-4.645321353768784</v>
       </c>
       <c r="G74">
-        <v>-6.627994716660089</v>
+        <v>-7.27936441478493</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.04751383103821</v>
       </c>
       <c r="E75">
-        <v>-5.999600678983759</v>
+        <v>-8.25180099890655</v>
       </c>
       <c r="F75">
-        <v>-5.924581559423102</v>
+        <v>-5.147088340666528</v>
       </c>
       <c r="G75">
-        <v>-6.160750940338431</v>
+        <v>-7.292613218033093</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.844325428467469</v>
       </c>
       <c r="E76">
-        <v>-6.654168954422471</v>
+        <v>-8.683088334923067</v>
       </c>
       <c r="F76">
-        <v>-6.085384239654542</v>
+        <v>-5.000745641818356</v>
       </c>
       <c r="G76">
-        <v>-6.444299165777009</v>
+        <v>-6.864847697267246</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.671054302348258</v>
       </c>
       <c r="E77">
-        <v>-8.088871032584578</v>
+        <v>-9.13780599545527</v>
       </c>
       <c r="F77">
-        <v>-5.377000056578725</v>
+        <v>-5.043742051860665</v>
       </c>
       <c r="G77">
-        <v>-6.861441145907335</v>
+        <v>-7.185093320008644</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.528841414926801</v>
       </c>
       <c r="E78">
-        <v>-7.425331850136672</v>
+        <v>-8.892530257777821</v>
       </c>
       <c r="F78">
-        <v>-5.870339233520387</v>
+        <v>-5.296117435001979</v>
       </c>
       <c r="G78">
-        <v>-6.595822835109451</v>
+        <v>-7.035973106737712</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.416891882455146</v>
       </c>
       <c r="E79">
-        <v>-8.624924614768549</v>
+        <v>-9.987402060982323</v>
       </c>
       <c r="F79">
-        <v>-6.14390922502973</v>
+        <v>-5.590561456694466</v>
       </c>
       <c r="G79">
-        <v>-6.451741272149291</v>
+        <v>-6.927893726517126</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.335970912354188</v>
       </c>
       <c r="E80">
-        <v>-10.15643641026663</v>
+        <v>-10.45522512529272</v>
       </c>
       <c r="F80">
-        <v>-5.877471476858491</v>
+        <v>-5.576505718603764</v>
       </c>
       <c r="G80">
-        <v>-5.289428596584412</v>
+        <v>-6.46418892337695</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.283241282099069</v>
       </c>
       <c r="E81">
-        <v>-9.800801761022257</v>
+        <v>-11.2971046711107</v>
       </c>
       <c r="F81">
-        <v>-6.117590335907984</v>
+        <v>-5.554013058515549</v>
       </c>
       <c r="G81">
-        <v>-5.732588154107871</v>
+        <v>-6.237654913215701</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.252980614750492</v>
       </c>
       <c r="E82">
-        <v>-11.43054974316873</v>
+        <v>-12.41710950505778</v>
       </c>
       <c r="F82">
-        <v>-6.152660098272904</v>
+        <v>-5.310201337584376</v>
       </c>
       <c r="G82">
-        <v>-5.314449699770224</v>
+        <v>-6.330436262499315</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.2368600008887</v>
       </c>
       <c r="E83">
-        <v>-12.98616660580965</v>
+        <v>-12.52819297246593</v>
       </c>
       <c r="F83">
-        <v>-6.340735946874115</v>
+        <v>-5.730410583472093</v>
       </c>
       <c r="G83">
-        <v>-5.625611185551862</v>
+        <v>-6.363475506981242</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.226646938739641</v>
       </c>
       <c r="E84">
-        <v>-11.72336540097871</v>
+        <v>-13.34968985677539</v>
       </c>
       <c r="F84">
-        <v>-6.670106009187136</v>
+        <v>-5.904269990706458</v>
       </c>
       <c r="G84">
-        <v>-5.562929316311301</v>
+        <v>-5.775032658466867</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.21147147399927</v>
       </c>
       <c r="E85">
-        <v>-13.76693892336812</v>
+        <v>-13.73879898588446</v>
       </c>
       <c r="F85">
-        <v>-6.639927342152046</v>
+        <v>-6.243410232351798</v>
       </c>
       <c r="G85">
-        <v>-5.983438121255067</v>
+        <v>-6.162111574555072</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.180929525054258</v>
       </c>
       <c r="E86">
-        <v>-15.15722119998899</v>
+        <v>-15.41260449165156</v>
       </c>
       <c r="F86">
-        <v>-7.113101157223658</v>
+        <v>-6.241116068829745</v>
       </c>
       <c r="G86">
-        <v>-6.415292165761914</v>
+        <v>-5.220254747541341</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.128152014638197</v>
       </c>
       <c r="E87">
-        <v>-16.46668832946898</v>
+        <v>-16.94382193633915</v>
       </c>
       <c r="F87">
-        <v>-6.56487104270289</v>
+        <v>-6.265486223636406</v>
       </c>
       <c r="G87">
-        <v>-6.451416838686442</v>
+        <v>-6.15058425498733</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.052143988622441</v>
       </c>
       <c r="E88">
-        <v>-16.94784322125796</v>
+        <v>-17.34340995430198</v>
       </c>
       <c r="F88">
-        <v>-6.808746133740377</v>
+        <v>-6.223990815327969</v>
       </c>
       <c r="G88">
-        <v>-5.49739044627035</v>
+        <v>-5.295778222928734</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-1.956552672132287</v>
       </c>
       <c r="E89">
-        <v>-18.0215987501647</v>
+        <v>-19.20107150478049</v>
       </c>
       <c r="F89">
-        <v>-7.045095921107132</v>
+        <v>-6.643392402997956</v>
       </c>
       <c r="G89">
-        <v>-5.653231066986002</v>
+        <v>-6.020205040014213</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-1.848545641917816</v>
       </c>
       <c r="E90">
-        <v>-20.8201504021649</v>
+        <v>-21.20680509836182</v>
       </c>
       <c r="F90">
-        <v>-6.690415092801572</v>
+        <v>-6.627042501385201</v>
       </c>
       <c r="G90">
-        <v>-5.965521448796531</v>
+        <v>-5.863943980015073</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-1.740751834932011</v>
       </c>
       <c r="E91">
-        <v>-22.56340911378764</v>
+        <v>-22.40861681525745</v>
       </c>
       <c r="F91">
-        <v>-7.358225426304568</v>
+        <v>-6.577756297653436</v>
       </c>
       <c r="G91">
-        <v>-4.811740049086355</v>
+        <v>-6.402506838889249</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-1.649458098566016</v>
       </c>
       <c r="E92">
-        <v>-24.8050218614805</v>
+        <v>-24.63112393111195</v>
       </c>
       <c r="F92">
-        <v>-7.307158646840485</v>
+        <v>-6.708493797183969</v>
       </c>
       <c r="G92">
-        <v>-6.275087251628241</v>
+        <v>-6.594448958710654</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-1.591649488232849</v>
       </c>
       <c r="E93">
-        <v>-26.63162713721442</v>
+        <v>-26.56408947586402</v>
       </c>
       <c r="F93">
-        <v>-7.097157155638275</v>
+        <v>-6.891869074957995</v>
       </c>
       <c r="G93">
-        <v>-6.805532652840124</v>
+        <v>-6.49694015039696</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-1.583661944037311</v>
       </c>
       <c r="E94">
-        <v>-29.45797003419969</v>
+        <v>-28.5013117861833</v>
       </c>
       <c r="F94">
-        <v>-7.679814633603093</v>
+        <v>-6.656109499365734</v>
       </c>
       <c r="G94">
-        <v>-6.388632342534164</v>
+        <v>-6.75185877801192</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-1.641732368105225</v>
       </c>
       <c r="E95">
-        <v>-30.06858041244595</v>
+        <v>-30.82094561255431</v>
       </c>
       <c r="F95">
-        <v>-6.910729343984934</v>
+        <v>-6.502064640406333</v>
       </c>
       <c r="G95">
-        <v>-7.767050809811587</v>
+        <v>-7.220291040182175</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-1.784447889100009</v>
       </c>
       <c r="E96">
-        <v>-33.23643591248268</v>
+        <v>-32.61510890049728</v>
       </c>
       <c r="F96">
-        <v>-6.959382260837259</v>
+        <v>-6.688499078998897</v>
       </c>
       <c r="G96">
-        <v>-7.503994861261098</v>
+        <v>-7.775409937298246</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-2.01117047259233</v>
       </c>
       <c r="E97">
-        <v>-35.41368545910452</v>
+        <v>-35.59581841945602</v>
       </c>
       <c r="F97">
-        <v>-7.231565565314314</v>
+        <v>-6.852014248290804</v>
       </c>
       <c r="G97">
-        <v>-8.146975636989426</v>
+        <v>-7.864205389752578</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-2.332284272365303</v>
       </c>
       <c r="E98">
-        <v>-37.54386831112764</v>
+        <v>-38.25322432934815</v>
       </c>
       <c r="F98">
-        <v>-6.755192181149389</v>
+        <v>-6.790298391680032</v>
       </c>
       <c r="G98">
-        <v>-8.449711784373619</v>
+        <v>-8.902279912319687</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-2.718143136937703</v>
       </c>
       <c r="E99">
-        <v>-41.27553467477836</v>
+        <v>-39.70429457681098</v>
       </c>
       <c r="F99">
-        <v>-7.769336713007337</v>
+        <v>-6.764319133193434</v>
       </c>
       <c r="G99">
-        <v>-8.912585640583439</v>
+        <v>-9.380312756553829</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.185471719638775</v>
       </c>
       <c r="E100">
-        <v>-43.00867903970497</v>
+        <v>-42.28254049681203</v>
       </c>
       <c r="F100">
-        <v>-6.86838237398642</v>
+        <v>-6.630641343566664</v>
       </c>
       <c r="G100">
-        <v>-9.328595414139334</v>
+        <v>-9.710218551178821</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.663331913598819</v>
       </c>
       <c r="E101">
-        <v>-45.26848266748664</v>
+        <v>-44.76797534202587</v>
       </c>
       <c r="F101">
-        <v>-7.388662129785629</v>
+        <v>-6.626945168215372</v>
       </c>
       <c r="G101">
-        <v>-8.669800162369906</v>
+        <v>-9.377194222655834</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.221784564008575</v>
       </c>
       <c r="E102">
-        <v>-47.25319734896136</v>
+        <v>-47.02984395395504</v>
       </c>
       <c r="F102">
-        <v>-7.088426991580171</v>
+        <v>-6.437635880551393</v>
       </c>
       <c r="G102">
-        <v>-10.24960242534674</v>
+        <v>-10.70796400798653</v>
       </c>
     </row>
   </sheetData>
